--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484628_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484628_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.9322</v>
+        <v>9.158300000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.392300000000001</v>
+        <v>9.420199999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4601</v>
+        <v>-0.2619</v>
       </c>
       <c r="G2" t="n">
         <v>4.8961</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1857</v>
+        <v>0.4118</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3077</v>
+        <v>0.3356</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1221</v>
+        <v>0.0761</v>
       </c>
       <c r="V2" t="n">
         <v>4.7668</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3254</v>
+        <v>3.0679</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7746</v>
+        <v>2.2693</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5508</v>
+        <v>0.7985</v>
       </c>
       <c r="G3" t="n">
         <v>1.4753</v>
@@ -688,13 +688,13 @@
         <v>1.4661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6056</v>
+        <v>0.1369</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6976</v>
+        <v>-0.2029</v>
       </c>
       <c r="U3" t="n">
-        <v>0.092</v>
+        <v>0.3397</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0104</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.16</v>
+        <v>1.1575</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9908</v>
+        <v>0.1122</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1692</v>
+        <v>1.0453</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1488</v>
@@ -766,13 +766,13 @@
         <v>2.7489</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9868</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5528</v>
+        <v>0.6742</v>
       </c>
       <c r="U4" t="n">
-        <v>0.434</v>
+        <v>0.3101</v>
       </c>
       <c r="V4" t="n">
         <v>0.3219</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6521</v>
+        <v>0.4981</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9304</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5825</v>
+        <v>1.3595</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1344</v>
@@ -844,13 +844,13 @@
         <v>1.4661</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6032</v>
+        <v>0.4493</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0384</v>
+        <v>0.0306</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6417</v>
+        <v>0.4187</v>
       </c>
       <c r="V5" t="n">
         <v>0.6335</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4417</v>
+        <v>-0.3707</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.942</v>
+        <v>-1.5984</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5003</v>
+        <v>1.2278</v>
       </c>
       <c r="G6" t="n">
         <v>-0.727</v>
@@ -922,13 +922,13 @@
         <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0158</v>
+        <v>0.0552</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6056</v>
+        <v>-0.2621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5898</v>
+        <v>0.3173</v>
       </c>
       <c r="V6" t="n">
         <v>0.3011</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6976</v>
+        <v>-0.472</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8313</v>
+        <v>-0.6801</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1337</v>
+        <v>0.208</v>
       </c>
       <c r="G7" t="n">
         <v>-0.7652</v>
@@ -1000,13 +1000,13 @@
         <v>0.5498</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4821</v>
+        <v>-0.2566</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2753</v>
+        <v>-0.1241</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9808</v>
+        <v>-1.2986</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2139</v>
+        <v>-0.1428</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1947</v>
+        <v>-1.1558</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.1964</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7314000000000001</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2116</v>
+        <v>0.2854</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9749</v>
+        <v>0.7402</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5326</v>
+        <v>1.288</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5577</v>
+        <v>-0.5478</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.032</v>
+        <v>-0.5437</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8012</v>
+        <v>-1.3769</v>
       </c>
       <c r="O8" t="n">
-        <v>0.7692</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7118</v>
+        <v>-0.1834</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2217</v>
+        <v>-0.0162</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4901</v>
+        <v>-0.1673</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.212</v>
+        <v>-0.945</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6231</v>
+        <v>0.9658</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.5889</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4475</v>
+        <v>-1.5763</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1183</v>
+        <v>0.4201</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3292</v>
+        <v>-1.9965</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1964</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.7314000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2854</v>
+        <v>0.2116</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7402</v>
+        <v>1.9749</v>
       </c>
       <c r="K9" t="n">
-        <v>1.288</v>
+        <v>2.5326</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5478</v>
+        <v>-0.5577</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5437</v>
+        <v>-1.032</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3769</v>
+        <v>-1.8012</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.7692</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3323</v>
+        <v>-0.3073</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9917</v>
+        <v>-0.0154</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3407</v>
+        <v>-0.2919</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.945</v>
+        <v>-2.212</v>
       </c>
       <c r="W9" t="n">
-        <v>0.9658</v>
+        <v>-0.6231</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.9109</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4916</v>
+        <v>-2.0985</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4519</v>
+        <v>-2.1084</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0397</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3595</v>
@@ -1234,13 +1234,13 @@
         <v>0.3665</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4986</v>
+        <v>-0.1056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5505</v>
+        <v>-0.207</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0519</v>
+        <v>0.1014</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.5486</v>
+        <v>-7.2273</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.3067</v>
+        <v>-6.6634</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2419</v>
+        <v>-0.5639</v>
       </c>
       <c r="G11" t="n">
         <v>-7.5878</v>
@@ -1312,13 +1312,13 @@
         <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4241</v>
+        <v>1.7453</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3168</v>
+        <v>0.9601</v>
       </c>
       <c r="U11" t="n">
-        <v>1.1073</v>
+        <v>0.7852</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5681</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5381</v>
+        <v>0.8384000000000018</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.209000000000001</v>
+        <v>0.1672999999999982</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6708999999999997</v>
+        <v>0.6708999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-5.2119</v>
@@ -1390,13 +1390,13 @@
         <v>13.7445</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5536</v>
+        <v>2.93</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2035000000000002</v>
+        <v>1.1728</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7569</v>
+        <v>1.7568</v>
       </c>
       <c r="V12" t="n">
         <v>1.2878</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.1756</v>
+        <v>6.3146</v>
       </c>
       <c r="E13" t="n">
-        <v>5.6217</v>
+        <v>4.7563</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5539</v>
+        <v>1.5583</v>
       </c>
       <c r="G13" t="n">
         <v>2.8618</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>1.75</v>
+        <v>0.8889</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3907</v>
+        <v>0.5253</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3593</v>
+        <v>0.3637</v>
       </c>
       <c r="V13" t="n">
         <v>1.4643</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7533</v>
+        <v>2.1837</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7248</v>
+        <v>2.0517</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0285</v>
+        <v>0.132</v>
       </c>
       <c r="G14" t="n">
         <v>0.9706</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6796</v>
+        <v>0.1099</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8597</v>
+        <v>0.1867</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1802</v>
+        <v>-0.0767</v>
       </c>
       <c r="V14" t="n">
         <v>0.1869</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>L. ASSARDO JOVANI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3006</v>
+        <v>0.4079</v>
       </c>
       <c r="E16" t="n">
-        <v>2.35</v>
+        <v>0.3889</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0494</v>
+        <v>0.019</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9424</v>
+        <v>0.8282</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0932</v>
+        <v>1.152</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1508</v>
+        <v>-0.3238</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5868</v>
+        <v>0.8711</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5451</v>
+        <v>0.7461</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0417</v>
+        <v>0.125</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6443</v>
+        <v>-0.043</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4519</v>
+        <v>0.4059</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1925</v>
+        <v>-0.4489</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9163</v>
+        <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3649</v>
+        <v>-0.1874</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3288</v>
+        <v>-0.4823</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0361</v>
+        <v>0.2949</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.0905</v>
+        <v>-0.9658</v>
       </c>
       <c r="W16" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.3574</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. ASSARDO JOVANI</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1603</v>
+        <v>0.3254</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1004</v>
+        <v>2.35</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0599</v>
+        <v>-2.0246</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8282</v>
+        <v>1.9424</v>
       </c>
       <c r="H17" t="n">
-        <v>1.152</v>
+        <v>2.0932</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3238</v>
+        <v>-0.1508</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8711</v>
+        <v>2.5868</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7461</v>
+        <v>2.5451</v>
       </c>
       <c r="L17" t="n">
-        <v>0.125</v>
+        <v>0.0417</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.043</v>
+        <v>-0.6443</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4059</v>
+        <v>-0.4519</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4489</v>
+        <v>-0.1925</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R17" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.435</v>
+        <v>0.3897</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7707000000000001</v>
+        <v>0.3288</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3357</v>
+        <v>0.0609</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9658</v>
+        <v>-1.0905</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.9658</v>
+        <v>-2.3574</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1653</v>
+        <v>0.1406</v>
       </c>
       <c r="E18" t="n">
         <v>-0.9829</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8176</v>
+        <v>1.1236</v>
       </c>
       <c r="G18" t="n">
         <v>0.9500999999999999</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3878</v>
+        <v>-0.0818</v>
       </c>
       <c r="T18" t="n">
         <v>-0.46</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0722</v>
+        <v>0.3782</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2774</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2481</v>
+        <v>-0.0325</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4117</v>
+        <v>-2.0271</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1636</v>
+        <v>1.9945</v>
       </c>
       <c r="G19" t="n">
         <v>0.1737</v>
@@ -1936,13 +1936,13 @@
         <v>0.9163</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1597</v>
+        <v>0.0558</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8808</v>
+        <v>-0.4962</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7211</v>
+        <v>0.552</v>
       </c>
       <c r="V19" t="n">
         <v>0.6543</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5848</v>
+        <v>-0.1202</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8042</v>
+        <v>-0.3234</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2194</v>
+        <v>0.2033</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8064</v>
@@ -2014,13 +2014,13 @@
         <v>2.0158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5097</v>
+        <v>-0.0451</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8273</v>
+        <v>-0.3465</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3175</v>
+        <v>0.3014</v>
       </c>
       <c r="V20" t="n">
         <v>1.4643</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. GONZALEZ MAS</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9494</v>
+        <v>-0.3504</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4829</v>
+        <v>-0.6737</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4665</v>
+        <v>0.3232</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9054</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2421</v>
+        <v>-0.7494</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6633</v>
+        <v>1.263</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2627</v>
+        <v>0.43</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3685</v>
+        <v>-0.9293</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6312</v>
+        <v>1.3593</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6427</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6106</v>
+        <v>0.1799</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0321</v>
+        <v>-0.0964</v>
       </c>
       <c r="P21" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1833</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2273</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2202</v>
+        <v>-0.5381</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0071</v>
+        <v>0.4462</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>M. GONZALEZ MAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9284</v>
+        <v>-0.658</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3467</v>
+        <v>-0.2906</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5816</v>
+        <v>-0.3674</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.9054</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7494</v>
+        <v>-0.2421</v>
       </c>
       <c r="I22" t="n">
-        <v>1.263</v>
+        <v>-0.6633</v>
       </c>
       <c r="J22" t="n">
-        <v>0.43</v>
+        <v>-0.2627</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9293</v>
+        <v>0.3685</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3593</v>
+        <v>-0.6312</v>
       </c>
       <c r="M22" t="n">
-        <v>0.08359999999999999</v>
+        <v>-0.6427</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1799</v>
+        <v>-0.6106</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0964</v>
+        <v>-0.0321</v>
       </c>
       <c r="P22" t="n">
         <v>0.1833</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.0158</v>
+        <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6697</v>
+        <v>0.0641</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2111</v>
+        <v>-0.0279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4586</v>
+        <v>0.092</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2354</v>
+        <v>-2.8589</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.2283</v>
+        <v>-1.9014</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.007</v>
+        <v>-0.9575</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7888</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8754</v>
+        <v>0.2519</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8416</v>
+        <v>0.1686</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0338</v>
+        <v>0.0833</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7159</v>
+        <v>-3.8664</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.1863</v>
+        <v>-4.994</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4705</v>
+        <v>1.1276</v>
       </c>
       <c r="G24" t="n">
         <v>-0.503</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8342</v>
+        <v>-0.9847</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8077</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0265</v>
+        <v>-0.3694</v>
       </c>
       <c r="V24" t="n">
         <v>0.1869</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.5377999999999998</v>
+        <v>2.461100000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6708000000000016</v>
+        <v>-0.6708999999999996</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2089</v>
+        <v>3.132</v>
       </c>
       <c r="G25" t="n">
         <v>5.2121</v>
@@ -2374,7 +2374,7 @@
         <v>9.859799999999998</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.647699999999999</v>
+        <v>-4.6477</v>
       </c>
       <c r="J25" t="n">
         <v>7.176399999999998</v>
@@ -2404,19 +2404,19 @@
         <v>11.9117</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5535</v>
+        <v>0.3694999999999998</v>
       </c>
       <c r="T25" t="n">
         <v>-1.757</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2032999999999998</v>
+        <v>2.1265</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2878</v>
       </c>
       <c r="W25" t="n">
-        <v>7.653899999999999</v>
+        <v>7.653900000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-8.9415</v>
